--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -877,7 +877,7 @@
         <v>128793171</v>
       </c>
       <c r="B4" t="n">
-        <v>91876</v>
+        <v>91877</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793170</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793169</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128793171</v>
       </c>
       <c r="B4" t="n">
-        <v>91877</v>
+        <v>91904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793170</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128793171</v>
       </c>
       <c r="B4" t="n">
-        <v>91904</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -877,7 +877,7 @@
         <v>128793171</v>
       </c>
       <c r="B4" t="n">
-        <v>91909</v>
+        <v>91914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -969,6 +969,652 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128919113</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91522</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fäbodliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>750045</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7160579</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128919051</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57716</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fäbodliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>750244</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7160928</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>färska ringhack på en gran</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128919091</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79120</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fäbodliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>750038</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7160574</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128918938</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57716</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fäbodliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>750215</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7160936</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128918978</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57716</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fäbodliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>750233</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7160922</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>färska ringhack på två olika granar</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128919162</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57716</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fäbodliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>750045</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7160579</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>sannolikt bohål i död gran med granticka</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793170</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793169</v>
       </c>
       <c r="B3" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128793171</v>
       </c>
       <c r="B4" t="n">
-        <v>91914</v>
+        <v>91918</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128919113</v>
       </c>
       <c r="B5" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>128919051</v>
       </c>
       <c r="B6" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>128919091</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>128918938</v>
       </c>
       <c r="B8" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>128918978</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>128919162</v>
       </c>
       <c r="B10" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793170</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793169</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128793171</v>
       </c>
       <c r="B4" t="n">
-        <v>91918</v>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128919113</v>
       </c>
       <c r="B5" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>128919051</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>128919091</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>128918938</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>128918978</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>128919162</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -877,7 +877,7 @@
         <v>128793171</v>
       </c>
       <c r="B4" t="n">
-        <v>91931</v>
+        <v>91934</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128919113</v>
       </c>
       <c r="B5" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793170</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128793171</v>
       </c>
       <c r="B4" t="n">
-        <v>91934</v>
+        <v>91937</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128919113</v>
       </c>
       <c r="B5" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>128919091</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793170</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793169</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128793171</v>
       </c>
       <c r="B4" t="n">
-        <v>91937</v>
+        <v>91944</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128919113</v>
       </c>
       <c r="B5" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>128919051</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>128919091</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>128918938</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>128918978</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>128919162</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -877,7 +877,7 @@
         <v>128793171</v>
       </c>
       <c r="B4" t="n">
-        <v>91944</v>
+        <v>91951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128919113</v>
       </c>
       <c r="B5" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793170</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793169</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128793171</v>
       </c>
       <c r="B4" t="n">
-        <v>91951</v>
+        <v>91953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128919113</v>
       </c>
       <c r="B5" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>128919051</v>
       </c>
       <c r="B6" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>128919091</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>128918938</v>
       </c>
       <c r="B8" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>128918978</v>
       </c>
       <c r="B9" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>128919162</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -877,7 +877,7 @@
         <v>128793171</v>
       </c>
       <c r="B4" t="n">
-        <v>91953</v>
+        <v>91962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>128919113</v>
       </c>
       <c r="B5" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>128919113</v>
       </c>
       <c r="B5" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -991,14 +991,10 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>128919113</v>
       </c>
       <c r="B5" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>128919091</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>128919113</v>
       </c>
       <c r="B5" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>128919091</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128918978</v>
+        <v>128919162</v>
       </c>
       <c r="B9" t="n">
         <v>57727</v>
@@ -1428,11 +1428,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1440,10 +1436,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750233</v>
+        <v>750045</v>
       </c>
       <c r="R9" t="n">
-        <v>7160922</v>
+        <v>7160579</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,7 +1476,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>färska ringhack på två olika granar</t>
+          <t>sannolikt bohål i död gran med granticka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1507,7 +1503,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128919162</v>
+        <v>128918978</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1538,7 +1534,11 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750045</v>
+        <v>750233</v>
       </c>
       <c r="R10" t="n">
-        <v>7160579</v>
+        <v>7160922</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>sannolikt bohål i död gran med granticka</t>
+          <t>färska ringhack på två olika granar</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>128919113</v>
       </c>
       <c r="B5" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128919162</v>
+        <v>128918978</v>
       </c>
       <c r="B9" t="n">
         <v>57727</v>
@@ -1428,7 +1428,11 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1436,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750045</v>
+        <v>750233</v>
       </c>
       <c r="R9" t="n">
-        <v>7160579</v>
+        <v>7160922</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,7 +1480,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sannolikt bohål i död gran med granticka</t>
+          <t>färska ringhack på två olika granar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1503,7 +1507,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128918978</v>
+        <v>128919162</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1534,11 +1538,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750233</v>
+        <v>750045</v>
       </c>
       <c r="R10" t="n">
-        <v>7160922</v>
+        <v>7160579</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>färska ringhack på två olika granar</t>
+          <t>sannolikt bohål i död gran med granticka</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1611,6 +1611,1391 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129627163</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fäbodliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>750290</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7160564</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>hål i tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129627419</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fäbodliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>750156</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7160792</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129627541</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fäbodliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>750177</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7160773</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129627619</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fäbodliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>750177</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7160773</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129627655</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fäbodliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>750193</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7160774</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129626964</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fäbodliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>750359</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7161026</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129627103</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fäbodliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>750339</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7160657</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>hål i granlåga</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129627131</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fäbodliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>750302</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7160589</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129627014</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fäbodliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>750408</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7160936</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129627063</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fäbodliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>750338</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7160827</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129627706</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fäbodliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>750195</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7160780</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129627078</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Fäbodliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>750375</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7160721</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129627022</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91517</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fäbodliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>750367</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7160885</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -2683,7 +2683,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627706</v>
+        <v>129627078</v>
       </c>
       <c r="B21" t="n">
         <v>79044</v>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>750195</v>
+        <v>750375</v>
       </c>
       <c r="R21" t="n">
-        <v>7160780</v>
+        <v>7160721</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2788,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129627078</v>
+        <v>129627706</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>750375</v>
+        <v>750195</v>
       </c>
       <c r="R22" t="n">
-        <v>7160721</v>
+        <v>7160780</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -1938,7 +1938,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129627619</v>
+        <v>129627655</v>
       </c>
       <c r="B14" t="n">
         <v>79044</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750177</v>
+        <v>750193</v>
       </c>
       <c r="R14" t="n">
-        <v>7160773</v>
+        <v>7160774</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2043,7 +2043,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129627655</v>
+        <v>129627619</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750193</v>
+        <v>750177</v>
       </c>
       <c r="R15" t="n">
-        <v>7160774</v>
+        <v>7160773</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -1938,7 +1938,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129627655</v>
+        <v>129627619</v>
       </c>
       <c r="B14" t="n">
         <v>79044</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750193</v>
+        <v>750177</v>
       </c>
       <c r="R14" t="n">
-        <v>7160774</v>
+        <v>7160773</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2043,7 +2043,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129627619</v>
+        <v>129627655</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750177</v>
+        <v>750193</v>
       </c>
       <c r="R15" t="n">
-        <v>7160773</v>
+        <v>7160774</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -1616,7 +1616,7 @@
         <v>129627163</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>129627419</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>129627541</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>129627619</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>129627655</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>129626964</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>129627103</v>
       </c>
       <c r="B17" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>129627131</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>129627014</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>129627063</v>
       </c>
       <c r="B20" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>129627078</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>129627706</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>129627022</v>
       </c>
       <c r="B23" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -1616,7 +1616,7 @@
         <v>129627163</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>129627419</v>
       </c>
       <c r="B12" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>129627541</v>
       </c>
       <c r="B13" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129627619</v>
+        <v>129626964</v>
       </c>
       <c r="B14" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750177</v>
+        <v>750359</v>
       </c>
       <c r="R14" t="n">
-        <v>7160773</v>
+        <v>7161026</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129627655</v>
+        <v>129627619</v>
       </c>
       <c r="B15" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750193</v>
+        <v>750177</v>
       </c>
       <c r="R15" t="n">
-        <v>7160774</v>
+        <v>7160773</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129626964</v>
+        <v>129627655</v>
       </c>
       <c r="B16" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750359</v>
+        <v>750193</v>
       </c>
       <c r="R16" t="n">
-        <v>7161026</v>
+        <v>7160774</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,7 +2256,7 @@
         <v>129627103</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>129627131</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>129627014</v>
       </c>
       <c r="B19" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>129627063</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>129627078</v>
       </c>
       <c r="B21" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>129627706</v>
       </c>
       <c r="B22" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>129627022</v>
       </c>
       <c r="B23" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -1616,7 +1616,7 @@
         <v>129627163</v>
       </c>
       <c r="B11" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>129627419</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>129627541</v>
       </c>
       <c r="B13" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129626964</v>
+        <v>129627619</v>
       </c>
       <c r="B14" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750359</v>
+        <v>750177</v>
       </c>
       <c r="R14" t="n">
-        <v>7161026</v>
+        <v>7160773</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129627619</v>
+        <v>129627655</v>
       </c>
       <c r="B15" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750177</v>
+        <v>750193</v>
       </c>
       <c r="R15" t="n">
-        <v>7160773</v>
+        <v>7160774</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129627655</v>
+        <v>129626964</v>
       </c>
       <c r="B16" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750193</v>
+        <v>750359</v>
       </c>
       <c r="R16" t="n">
-        <v>7160774</v>
+        <v>7161026</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,7 +2256,7 @@
         <v>129627103</v>
       </c>
       <c r="B17" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>129627131</v>
       </c>
       <c r="B18" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>129627014</v>
       </c>
       <c r="B19" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>129627063</v>
       </c>
       <c r="B20" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>129627078</v>
       </c>
       <c r="B21" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>129627706</v>
       </c>
       <c r="B22" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>129627022</v>
       </c>
       <c r="B23" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -1726,7 +1726,7 @@
         <v>129627419</v>
       </c>
       <c r="B12" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>129627619</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>129627655</v>
       </c>
       <c r="B15" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>129626964</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>129627014</v>
       </c>
       <c r="B19" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>129627078</v>
       </c>
       <c r="B21" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>129627706</v>
       </c>
       <c r="B22" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>129627022</v>
       </c>
       <c r="B23" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -2683,7 +2683,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627078</v>
+        <v>129627706</v>
       </c>
       <c r="B21" t="n">
         <v>79081</v>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>750375</v>
+        <v>750195</v>
       </c>
       <c r="R21" t="n">
-        <v>7160721</v>
+        <v>7160780</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2788,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129627706</v>
+        <v>129627078</v>
       </c>
       <c r="B22" t="n">
         <v>79081</v>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>750195</v>
+        <v>750375</v>
       </c>
       <c r="R22" t="n">
-        <v>7160780</v>
+        <v>7160721</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2896,7 +2896,7 @@
         <v>129627022</v>
       </c>
       <c r="B23" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -2683,7 +2683,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627706</v>
+        <v>129627078</v>
       </c>
       <c r="B21" t="n">
         <v>79081</v>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>750195</v>
+        <v>750375</v>
       </c>
       <c r="R21" t="n">
-        <v>7160780</v>
+        <v>7160721</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2788,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129627078</v>
+        <v>129627706</v>
       </c>
       <c r="B22" t="n">
         <v>79081</v>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>750375</v>
+        <v>750195</v>
       </c>
       <c r="R22" t="n">
-        <v>7160721</v>
+        <v>7160780</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2896,7 +2896,7 @@
         <v>129627022</v>
       </c>
       <c r="B23" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -1938,7 +1938,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129627619</v>
+        <v>129627655</v>
       </c>
       <c r="B14" t="n">
         <v>79081</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750177</v>
+        <v>750193</v>
       </c>
       <c r="R14" t="n">
-        <v>7160773</v>
+        <v>7160774</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2043,7 +2043,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129627655</v>
+        <v>129626964</v>
       </c>
       <c r="B15" t="n">
         <v>79081</v>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750193</v>
+        <v>750359</v>
       </c>
       <c r="R15" t="n">
-        <v>7160774</v>
+        <v>7161026</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129626964</v>
+        <v>129627619</v>
       </c>
       <c r="B16" t="n">
         <v>79081</v>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750359</v>
+        <v>750177</v>
       </c>
       <c r="R16" t="n">
-        <v>7161026</v>
+        <v>7160773</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2683,7 +2683,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627078</v>
+        <v>129627706</v>
       </c>
       <c r="B21" t="n">
         <v>79081</v>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>750375</v>
+        <v>750195</v>
       </c>
       <c r="R21" t="n">
-        <v>7160721</v>
+        <v>7160780</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2788,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129627706</v>
+        <v>129627078</v>
       </c>
       <c r="B22" t="n">
         <v>79081</v>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>750195</v>
+        <v>750375</v>
       </c>
       <c r="R22" t="n">
-        <v>7160780</v>
+        <v>7160721</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -1616,7 +1616,7 @@
         <v>129627163</v>
       </c>
       <c r="B11" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>129627419</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>129627541</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129627655</v>
+        <v>129627619</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750193</v>
+        <v>750177</v>
       </c>
       <c r="R14" t="n">
-        <v>7160774</v>
+        <v>7160773</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129626964</v>
+        <v>129627655</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750359</v>
+        <v>750193</v>
       </c>
       <c r="R15" t="n">
-        <v>7161026</v>
+        <v>7160774</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129627619</v>
+        <v>129626964</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750177</v>
+        <v>750359</v>
       </c>
       <c r="R16" t="n">
-        <v>7160773</v>
+        <v>7161026</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,7 +2256,7 @@
         <v>129627103</v>
       </c>
       <c r="B17" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>129627131</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>129627014</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>129627063</v>
       </c>
       <c r="B20" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627706</v>
+        <v>129627078</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>750195</v>
+        <v>750375</v>
       </c>
       <c r="R21" t="n">
-        <v>7160780</v>
+        <v>7160721</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129627078</v>
+        <v>129627706</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>750375</v>
+        <v>750195</v>
       </c>
       <c r="R22" t="n">
-        <v>7160721</v>
+        <v>7160780</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2896,7 +2896,7 @@
         <v>129627022</v>
       </c>
       <c r="B23" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -1616,7 +1616,7 @@
         <v>129627163</v>
       </c>
       <c r="B11" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>129627419</v>
       </c>
       <c r="B12" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>129627541</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>129627619</v>
       </c>
       <c r="B14" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129627655</v>
+        <v>129626964</v>
       </c>
       <c r="B15" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750193</v>
+        <v>750359</v>
       </c>
       <c r="R15" t="n">
-        <v>7160774</v>
+        <v>7161026</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129626964</v>
+        <v>129627655</v>
       </c>
       <c r="B16" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750359</v>
+        <v>750193</v>
       </c>
       <c r="R16" t="n">
-        <v>7161026</v>
+        <v>7160774</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,7 +2256,7 @@
         <v>129627103</v>
       </c>
       <c r="B17" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>129627131</v>
       </c>
       <c r="B18" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>129627014</v>
       </c>
       <c r="B19" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>129627063</v>
       </c>
       <c r="B20" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>129627078</v>
       </c>
       <c r="B21" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>129627706</v>
       </c>
       <c r="B22" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>129627022</v>
       </c>
       <c r="B23" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 45973-2025 artfynd.xlsx
+++ b/artfynd/A 45973-2025 artfynd.xlsx
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG13" t="b">
         <v>0</v>
